--- a/data/trans_camb/IQ26A_R2-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IQ26A_R2-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>3.613382861826385</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4.407687575914519</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.661866425686769</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>7.381859434679562</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>3.171480388841225</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>5.608208224919539</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-1.067985584854292</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.319286642383096</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.022413950105901</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.553942954708249</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-0.1926451128605471</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-2.524647131858983</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>9.004446708052148</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>22.27834503088306</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.087205969114491</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>25.26008806539371</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>6.605900522566523</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>18.08802846787653</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.321950392092465</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.3927224978782081</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.2573034248295673</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.7135510992680482</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.2937050373222366</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.5193659755256113</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.08716009348097016</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.4935829947940938</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.175020371190887</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.3414795737165972</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.02190574955174423</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2218309412441779</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>1.057653888242698</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2.328478480618993</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.8426776679224747</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2.890602251675534</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.6949318072094707</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.774957810611692</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>4.555714828524006</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.7808672790769411</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5.489025494235211</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.418062014470014</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>5.038146620164169</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.717966500017829</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-1.480235043029532</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.26709733058633</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.5134382835252712</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.631742931559898</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.8348954793430957</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-4.053098892266796</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>10.4273057159898</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>13.4269083292788</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10.45562342405558</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>14.5942261558116</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>8.896919151562969</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>10.13779539366742</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.389571705023592</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.06677410873096619</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.6173149399300427</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.2719436826768928</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.4900307337711092</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1670964440035468</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.1188956855600186</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.5877207694942587</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.03449600179857486</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.6043425129507576</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.08402094094657632</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.382423451191546</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>1.223508415608982</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1.456093369909839</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1.509994843007308</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1.999913510867726</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.066273958247376</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.128306605769046</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>1.292581118890007</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>8.090513532763513</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>7.077203698567507</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>13.71634105486926</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>4.224705061718286</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>10.53689304289975</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-4.562805042386115</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.4044917516792503</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.2059213364722076</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>4.049070053021828</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-0.1921238066345527</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>4.028343095234507</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>7.488886971266981</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>18.73742115256144</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>13.07982552383938</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>26.89344605078051</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>9.120250731653837</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>18.3038962643701</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.1279725252241418</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.8010046193750292</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.692212308693108</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1.341577904608697</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.4157545307611029</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1.036938900759372</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.3731786094209044</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.09465519476217253</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.007958088334118292</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0.2514366862778332</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.01812118438420521</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.33457519375858</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>1.000475453696225</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>2.313165764792783</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1.776597761685515</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>3.201712564410462</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1.088554750092035</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>2.153117628719995</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>4.016984293430517</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>15.04245400879731</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.5145711180263829</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>18.39850701258533</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>1.931811736384745</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>16.72133607092233</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-4.441670122482859</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1.958759799145573</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-9.949797281823102</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>3.976002237885224</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-4.397744522452077</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>7.403152539706024</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>12.00761506740497</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>28.89005955562509</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>9.607287732766697</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>33.42787205119487</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>8.413249035197547</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>26.89620073674215</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>0.342943985175358</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>1.284226859694397</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.03133725744443117</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>1.120464656193544</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.1392246806882397</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1.205098111429659</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.2877022659280625</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.09838459284174851</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.47415645166189</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0.1412065947843854</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.2620419337072414</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.3997641043533383</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>1.639610133666919</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>3.5113171356569</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.9039828745865339</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>2.731019178160377</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.8177499740142434</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>2.303107167968663</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>3.465634182364244</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>6.953275476687567</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>4.120678460775268</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>12.45500021480725</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>3.78613874484823</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>9.347211239230601</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>0.5860708789662229</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1.799932213207583</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>1.147664272132854</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>6.782380454452078</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1.721708054183436</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>5.663197750373459</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>6.622379785715204</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>13.24348615751917</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>6.90294850444681</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>18.81826985359639</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>5.892904816010422</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>14.07831626140718</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>0.3098778752871567</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.6217235050273912</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.3903416360465058</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>1.179831235823423</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.3480937754397229</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.8593731686467337</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>0.04477367229096805</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.1458036206371534</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0.1002920825125338</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>0.6121608608331582</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0.1455626814134993</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>0.4879637050332056</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.704869210938869</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>1.286544030529252</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.7727421760647628</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1.981261497144095</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.5973742100139773</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>1.357399774590792</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
